--- a/main/ig/all-profiles.xlsx
+++ b/main/ig/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-25T15:44:45+00:00</t>
+    <t>2025-11-27T10:20:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -736,7 +736,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -940,7 +940,7 @@
     <t>Group.managingEntity</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization|RelatedPerson|Practitioner|PractitionerRole)
+    <t xml:space="preserve">Reference(Organization|4.0.1|RelatedPerson|4.0.1|Practitioner|4.0.1|PractitionerRole|4.0.1)
 </t>
   </si>
   <si>
@@ -1108,7 +1108,7 @@
     <t>Group.member.entity</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|Practitioner|PractitionerRole|Device|Medication|Substance|Group)
+    <t xml:space="preserve">Reference(Patient|4.0.1|Practitioner|4.0.1|PractitionerRole|4.0.1|Device|4.0.1|Medication|4.0.1|Substance|4.0.1|Group|4.0.1)
 </t>
   </si>
   <si>
@@ -1540,7 +1540,7 @@
     <t>Physical form of the location.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/location-physical-type</t>
+    <t>http://hl7.org/fhir/ValueSet/location-physical-type|4.0.1</t>
   </si>
   <si>
     <t>Location.position</t>
@@ -1601,7 +1601,7 @@
     <t>Location.managingOrganization</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -1620,7 +1620,7 @@
     <t>Location.partOf</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Location)
+    <t xml:space="preserve">Reference(Location|4.0.1)
 </t>
   </si>
   <si>
@@ -1713,7 +1713,7 @@
     <t>Location.endpoint</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Endpoint)
+    <t xml:space="preserve">Reference(Endpoint|4.0.1)
 </t>
   </si>
   <si>
@@ -1983,8 +1983,8 @@
     <t>Allows identification of the research study as it is known by various participating systems and in a way that remains consistent across servers.</t>
   </si>
   <si>
-    <t xml:space="preserve">value:use}
-</t>
+    <t>value:use}
+value:system}</t>
   </si>
   <si>
     <t>Slicing pour les différents identifiants de l'essai clinique</t>
@@ -2062,7 +2062,7 @@
     <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -2253,7 +2253,7 @@
     <t>ResearchStudy.protocol</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(PlanDefinition)
+    <t xml:space="preserve">Reference(PlanDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -2270,7 +2270,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(ResearchStudy)
+    <t xml:space="preserve">Reference(ResearchStudy|4.0.1)
 </t>
   </si>
   <si>
@@ -2310,7 +2310,7 @@
     <t>Codes for the main intent of the study.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/research-study-prim-purp-type</t>
+    <t>http://hl7.org/fhir/ValueSet/research-study-prim-purp-type|4.0.1</t>
   </si>
   <si>
     <t>ResearchStudy.phase</t>
@@ -2361,7 +2361,7 @@
     <t>Identification of the condition or diagnosis.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/condition-code</t>
+    <t>http://hl7.org/fhir/ValueSet/condition-code|4.0.1</t>
   </si>
   <si>
     <t>Slicing pour apporter des précisions sur le sujet / Health Condition(s) or Problem(s) Studied. Dans le CTIS, il y a un champ texte ouvert (obligatoire) pour indiquer la pathologie et éventuellement des précisons. Un code MedDRA peut-être ajouté mais il est optionnel.
@@ -2695,7 +2695,7 @@
     <t>Countries and regions within which this artifact is targeted for use.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/jurisdiction</t>
+    <t>http://hl7.org/fhir/ValueSet/jurisdiction|4.0.1</t>
   </si>
   <si>
     <t>ResearchStudy.description</t>
@@ -2773,7 +2773,7 @@
     <t>ResearchStudy.principalInvestigator</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole)
+    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1)
 </t>
   </si>
   <si>
@@ -2808,7 +2808,7 @@
     <t>Codes for why the study ended prematurely.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/research-study-reason-stopped</t>
+    <t>http://hl7.org/fhir/ValueSet/research-study-reason-stopped|4.0.1</t>
   </si>
   <si>
     <t>ResearchStudy.note</t>
@@ -2921,7 +2921,7 @@
     <t>Codes for the kind of study objective.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/research-study-objective-type</t>
+    <t>http://hl7.org/fhir/ValueSet/research-study-objective-type|4.0.1</t>
   </si>
   <si>
     <t>https://interop.esante.gouv.fr/ig/fhir/eclaire/StructureDefinition/eclaire-review-date</t>

--- a/main/ig/all-profiles.xlsx
+++ b/main/ig/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-27T10:20:46+00:00</t>
+    <t>2025-11-27T15:06:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
